--- a/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -1,34 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8012D23-0F8A-4BBC-99AC-E0EDBD66A4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Quality Checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>check_group</t>
+  </si>
+  <si>
+    <t>check_name</t>
+  </si>
+  <si>
+    <t>check_label</t>
+  </si>
+  <si>
+    <t>variables</t>
+  </si>
+  <si>
+    <t>statistical_test</t>
+  </si>
+  <si>
+    <t>threshold_expression</t>
+  </si>
+  <si>
+    <t>penalty_score</t>
+  </si>
+  <si>
+    <t>test_params</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +80,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,165 +382,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>check_group</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>check_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>check_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>check_type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>mort_01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Death date validity</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>validity</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>death_date</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>is.Date(death_date) &amp; !is.na(death_date)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Death date must be a valid date</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>mort_02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Death age consistency</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>consistency</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>age_at_death</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>age_at_death &gt;= 0 &amp; age_at_death &lt;= 120</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Age at death must be between 0 and 120 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mort_03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Death rate plausibility</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>plausibility</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>deaths</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>deaths/person_time &lt; 0.1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Death rate should be plausible (less than 10 per 100 person-time)</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8012D23-0F8A-4BBC-99AC-E0EDBD66A4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A670D4FD-F66C-46BD-9223-9987D70B2CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>check_group</t>
   </si>
@@ -44,6 +44,42 @@
   </si>
   <si>
     <t>test_params</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>Sex Ratio</t>
+  </si>
+  <si>
+    <t>Age Ratio 0-1 : 2-5 years</t>
+  </si>
+  <si>
+    <t>Age Ratio 0-5 : 5-10 years</t>
+  </si>
+  <si>
+    <t>Age Ratio 0-5 : 5 plus years</t>
+  </si>
+  <si>
+    <t>Mean Household Size</t>
+  </si>
+  <si>
+    <t>Mean Deaths per Household</t>
+  </si>
+  <si>
+    <t>Mean Borths per Household</t>
+  </si>
+  <si>
+    <t>Mean Joiners per Household</t>
+  </si>
+  <si>
+    <t>Mean Leavers per Household</t>
+  </si>
+  <si>
+    <t>age_years</t>
+  </si>
+  <si>
+    <t>num_male,num_female</t>
   </si>
 </sst>
 </file>
@@ -383,13 +419,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -422,6 +458,60 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A670D4FD-F66C-46BD-9223-9987D70B2CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD59619-DB02-4F9D-9093-D9B2A5932208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>check_group</t>
   </si>
@@ -76,10 +76,13 @@
     <t>Mean Leavers per Household</t>
   </si>
   <si>
-    <t>age_years</t>
-  </si>
-  <si>
     <t>num_male,num_female</t>
+  </si>
+  <si>
+    <t>num_children_2_5yr,num_5plus</t>
+  </si>
+  <si>
+    <t>num_children_under5,num_5plus</t>
   </si>
 </sst>
 </file>
@@ -466,48 +469,75 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>

--- a/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD59619-DB02-4F9D-9093-D9B2A5932208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E10055E-5D02-4336-A707-F5A2603E3E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>check_group</t>
   </si>
@@ -46,9 +46,6 @@
     <t>test_params</t>
   </si>
   <si>
-    <t>Mortality</t>
-  </si>
-  <si>
     <t>Sex Ratio</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>Mean Deaths per Household</t>
   </si>
   <si>
-    <t>Mean Borths per Household</t>
-  </si>
-  <si>
     <t>Mean Joiners per Household</t>
   </si>
   <si>
@@ -83,6 +77,24 @@
   </si>
   <si>
     <t>num_children_under5,num_5plus</t>
+  </si>
+  <si>
+    <t>hh_size</t>
+  </si>
+  <si>
+    <t>Overall Mortality</t>
+  </si>
+  <si>
+    <t>num_deaths</t>
+  </si>
+  <si>
+    <t>Mean Births per Household</t>
+  </si>
+  <si>
+    <t>num_join</t>
+  </si>
+  <si>
+    <t>num_left</t>
   </si>
 </sst>
 </file>
@@ -428,7 +440,7 @@
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -463,83 +475,95 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E10055E-5D02-4336-A707-F5A2603E3E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8147CA4-F776-44C7-B010-DE9F922313F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>check_group</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Overall Mortality</t>
   </si>
   <si>
-    <t>num_deaths</t>
-  </si>
-  <si>
     <t>Mean Births per Household</t>
   </si>
   <si>
@@ -95,6 +92,15 @@
   </si>
   <si>
     <t>num_left</t>
+  </si>
+  <si>
+    <t>num_births</t>
+  </si>
+  <si>
+    <t>num_died</t>
+  </si>
+  <si>
+    <t>num_children_under5,</t>
   </si>
 </sst>
 </file>
@@ -502,6 +508,9 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -533,7 +542,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -541,7 +550,10 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -552,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -563,7 +575,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
